--- a/RPAs/study-status-report/reports/study_status_management_sample.xlsx
+++ b/RPAs/study-status-report/reports/study_status_management_sample.xlsx
@@ -5,6 +5,7 @@
     <sheet name="학생 현황" sheetId="1" r:id="rId1"/>
     <sheet name="상태 변화 기록" sheetId="2" r:id="rId2"/>
     <sheet name="일일 리포트" sheetId="3" r:id="rId3"/>
+    <sheet name="리포트 데이터" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -34,6 +35,203 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:t>상태별 종합</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'리포트 데이터'!$A$2:$A$6</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'리포트 데이터'!$B$2:$B$6</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="123456"/>
+        <c:axId val="654321"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="123456"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="654321"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="654321"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="123456"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:t>학생별 자리 이탈 정도</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'리포트 데이터'!$A$9:$A$11</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'리포트 데이터'!$B$9:$B$11</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="123456"/>
+        <c:axId val="654321"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="123456"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="654321"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="654321"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="123456"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="18"/>
@@ -57,11 +255,6 @@
           <t/>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -79,11 +272,6 @@
           <t>학생 상태</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>상태 판단 근거</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -101,11 +289,6 @@
           <t>착석</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>배정 좌석 복귀 확인</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -123,11 +306,6 @@
           <t>오착석</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>다른 좌석에서 식별됨</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -145,15 +323,10 @@
           <t>판단 보류</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>좌석 관측 근거 부족</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -191,16 +364,6 @@
           <t/>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -228,16 +391,6 @@
           <t>학생 상태</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>상태 판단 근거</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>원본 근거 코드</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -265,16 +418,6 @@
           <t>미착석</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>공부 시간 중 배정 좌석 미착석</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>SEAT_VACANT_BEYOND_GRACE</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -302,16 +445,6 @@
           <t>오착석</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>다른 좌석에서 식별됨</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>IDENTIFIED_AT_OTHER_SEAT</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -339,16 +472,6 @@
           <t>판단 보류</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>좌석 관측 근거 부족</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SEAT_NOT_OBSERVED</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -376,20 +499,10 @@
           <t>착석</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>배정 좌석 복귀 확인</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>IDENTIFIED_AT_ASSIGNED_SEAT</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -417,229 +530,253 @@
           <t/>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>지표</t>
+          <t>상태별 종합과 학생별 자리 이탈 정도를 그래프로 표시합니다.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>값</t>
+          <t/>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>비고</t>
+          <t/>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>총 상태 변화 건수</t>
+          <t>상태별 종합</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>학생별 자리 이탈 정도</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="8" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>건수</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>미착석 건수</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>오착석 건수</t>
         </is>
       </c>
       <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>중복 제거 후 기록 기준</t>
-        </is>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>영향 학생 수</t>
+          <t>좌석 외 위치 건수</t>
         </is>
       </c>
       <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>상태 변화가 1회 이상 기록된 학생</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>자리 이탈률</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ABSENT + WRONG_SEAT + IN_CLASSROOM / 전체 상태 변화</t>
-        </is>
+          <t>판단 보류 건수</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>미착석 건수</t>
+          <t>정상 착석 복귀 건수</t>
         </is>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>배정 좌석 미착석</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>오착석 건수</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>다른 좌석 착석</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>좌석 외 위치 건수</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>0</v>
+          <t>학생명</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>자리 이탈 건수</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>강의실 안이지만 좌석 외 위치</t>
+          <t>자리 이탈률(%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>판단 보류 건수</t>
+          <t>김민준</t>
         </is>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>근거 부족</t>
-        </is>
+      <c r="C9">
+        <v>50.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>정상 착석 복귀 건수</t>
+          <t>박지호</t>
         </is>
       </c>
       <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>이서연</t>
+        </is>
+      </c>
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>배정 좌석 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>학생별 상태 변화 건수</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>학생명</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>건수</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>김민준</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>박지호</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>이서연</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C11">
+        <v>100.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
 </worksheet>
 </file>